--- a/ensaios/protocolo-ensaio-estanqueidade.xlsx
+++ b/ensaios/protocolo-ensaio-estanqueidade.xlsx
@@ -2506,7 +2506,7 @@
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="14">
-        <f>IF(OR(C5="",D5=""),"",C5-D5)</f>
+        <f>IF(OR(C5="",D5=""),"",ROUND(C5-D5,2))</f>
         <v/>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -2531,7 +2531,7 @@
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="14">
-        <f>IF(OR(C6="",D6=""),"",C6-D6)</f>
+        <f>IF(OR(C6="",D6=""),"",ROUND(C6-D6,2))</f>
         <v/>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -2556,7 +2556,7 @@
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="14">
-        <f>IF(OR(C7="",D7=""),"",C7-D7)</f>
+        <f>IF(OR(C7="",D7=""),"",ROUND(C7-D7,2))</f>
         <v/>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -2581,7 +2581,7 @@
       <c r="C8" s="12" t="n"/>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="14">
-        <f>IF(OR(C8="",D8=""),"",C8-D8)</f>
+        <f>IF(OR(C8="",D8=""),"",ROUND(C8-D8,2))</f>
         <v/>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -2606,7 +2606,7 @@
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="14">
-        <f>IF(OR(C9="",D9=""),"",C9-D9)</f>
+        <f>IF(OR(C9="",D9=""),"",ROUND(C9-D9,2))</f>
         <v/>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -2631,7 +2631,7 @@
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="14">
-        <f>IF(OR(C10="",D10=""),"",C10-D10)</f>
+        <f>IF(OR(C10="",D10=""),"",ROUND(C10-D10,2))</f>
         <v/>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -2656,7 +2656,7 @@
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="14">
-        <f>IF(OR(C11="",D11=""),"",C11-D11)</f>
+        <f>IF(OR(C11="",D11=""),"",ROUND(C11-D11,2))</f>
         <v/>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -2681,7 +2681,7 @@
       <c r="C12" s="12" t="n"/>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="14">
-        <f>IF(OR(C12="",D12=""),"",C12-D12)</f>
+        <f>IF(OR(C12="",D12=""),"",ROUND(C12-D12,2))</f>
         <v/>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -2706,7 +2706,7 @@
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="14">
-        <f>IF(OR(C13="",D13=""),"",C13-D13)</f>
+        <f>IF(OR(C13="",D13=""),"",ROUND(C13-D13,2))</f>
         <v/>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -2731,7 +2731,7 @@
       <c r="C14" s="12" t="n"/>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="14">
-        <f>IF(OR(C14="",D14=""),"",C14-D14)</f>
+        <f>IF(OR(C14="",D14=""),"",ROUND(C14-D14,2))</f>
         <v/>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -2756,7 +2756,7 @@
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="14">
-        <f>IF(OR(C15="",D15=""),"",C15-D15)</f>
+        <f>IF(OR(C15="",D15=""),"",ROUND(C15-D15,2))</f>
         <v/>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -2781,7 +2781,7 @@
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="14">
-        <f>IF(OR(C16="",D16=""),"",C16-D16)</f>
+        <f>IF(OR(C16="",D16=""),"",ROUND(C16-D16,2))</f>
         <v/>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -2806,7 +2806,7 @@
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="14">
-        <f>IF(OR(C17="",D17=""),"",C17-D17)</f>
+        <f>IF(OR(C17="",D17=""),"",ROUND(C17-D17,2))</f>
         <v/>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -2831,7 +2831,7 @@
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="14">
-        <f>IF(OR(C18="",D18=""),"",C18-D18)</f>
+        <f>IF(OR(C18="",D18=""),"",ROUND(C18-D18,2))</f>
         <v/>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -2856,7 +2856,7 @@
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="14">
-        <f>IF(OR(C19="",D19=""),"",C19-D19)</f>
+        <f>IF(OR(C19="",D19=""),"",ROUND(C19-D19,2))</f>
         <v/>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -2881,7 +2881,7 @@
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="14">
-        <f>IF(OR(C20="",D20=""),"",C20-D20)</f>
+        <f>IF(OR(C20="",D20=""),"",ROUND(C20-D20,2))</f>
         <v/>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="14">
-        <f>IF(OR(C21="",D21=""),"",C21-D21)</f>
+        <f>IF(OR(C21="",D21=""),"",ROUND(C21-D21,2))</f>
         <v/>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -2931,7 +2931,7 @@
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="12" t="n"/>
       <c r="E22" s="14">
-        <f>IF(OR(C22="",D22=""),"",C22-D22)</f>
+        <f>IF(OR(C22="",D22=""),"",ROUND(C22-D22,2))</f>
         <v/>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -2956,7 +2956,7 @@
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="12" t="n"/>
       <c r="E23" s="14">
-        <f>IF(OR(C23="",D23=""),"",C23-D23)</f>
+        <f>IF(OR(C23="",D23=""),"",ROUND(C23-D23,2))</f>
         <v/>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -2981,7 +2981,7 @@
       <c r="C24" s="12" t="n"/>
       <c r="D24" s="12" t="n"/>
       <c r="E24" s="14">
-        <f>IF(OR(C24="",D24=""),"",C24-D24)</f>
+        <f>IF(OR(C24="",D24=""),"",ROUND(C24-D24,2))</f>
         <v/>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -3006,7 +3006,7 @@
       <c r="C25" s="12" t="n"/>
       <c r="D25" s="12" t="n"/>
       <c r="E25" s="14">
-        <f>IF(OR(C25="",D25=""),"",C25-D25)</f>
+        <f>IF(OR(C25="",D25=""),"",ROUND(C25-D25,2))</f>
         <v/>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -3031,7 +3031,7 @@
       <c r="C26" s="12" t="n"/>
       <c r="D26" s="12" t="n"/>
       <c r="E26" s="14">
-        <f>IF(OR(C26="",D26=""),"",C26-D26)</f>
+        <f>IF(OR(C26="",D26=""),"",ROUND(C26-D26,2))</f>
         <v/>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -3056,7 +3056,7 @@
       <c r="C27" s="12" t="n"/>
       <c r="D27" s="12" t="n"/>
       <c r="E27" s="14">
-        <f>IF(OR(C27="",D27=""),"",C27-D27)</f>
+        <f>IF(OR(C27="",D27=""),"",ROUND(C27-D27,2))</f>
         <v/>
       </c>
       <c r="F27" s="12" t="n"/>
@@ -3081,7 +3081,7 @@
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="12" t="n"/>
       <c r="E28" s="14">
-        <f>IF(OR(C28="",D28=""),"",C28-D28)</f>
+        <f>IF(OR(C28="",D28=""),"",ROUND(C28-D28,2))</f>
         <v/>
       </c>
       <c r="F28" s="12" t="n"/>
@@ -3106,7 +3106,7 @@
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="14">
-        <f>IF(OR(C29="",D29=""),"",C29-D29)</f>
+        <f>IF(OR(C29="",D29=""),"",ROUND(C29-D29,2))</f>
         <v/>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -3131,7 +3131,7 @@
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="14">
-        <f>IF(OR(C30="",D30=""),"",C30-D30)</f>
+        <f>IF(OR(C30="",D30=""),"",ROUND(C30-D30,2))</f>
         <v/>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -3156,7 +3156,7 @@
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="12" t="n"/>
       <c r="E31" s="14">
-        <f>IF(OR(C31="",D31=""),"",C31-D31)</f>
+        <f>IF(OR(C31="",D31=""),"",ROUND(C31-D31,2))</f>
         <v/>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -3181,7 +3181,7 @@
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="14">
-        <f>IF(OR(C32="",D32=""),"",C32-D32)</f>
+        <f>IF(OR(C32="",D32=""),"",ROUND(C32-D32,2))</f>
         <v/>
       </c>
       <c r="F32" s="12" t="n"/>
@@ -3206,7 +3206,7 @@
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="14">
-        <f>IF(OR(C33="",D33=""),"",C33-D33)</f>
+        <f>IF(OR(C33="",D33=""),"",ROUND(C33-D33,2))</f>
         <v/>
       </c>
       <c r="F33" s="12" t="n"/>
@@ -3231,7 +3231,7 @@
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="12" t="n"/>
       <c r="E34" s="14">
-        <f>IF(OR(C34="",D34=""),"",C34-D34)</f>
+        <f>IF(OR(C34="",D34=""),"",ROUND(C34-D34,2))</f>
         <v/>
       </c>
       <c r="F34" s="12" t="n"/>
@@ -3256,7 +3256,7 @@
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="12" t="n"/>
       <c r="E35" s="14">
-        <f>IF(OR(C35="",D35=""),"",C35-D35)</f>
+        <f>IF(OR(C35="",D35=""),"",ROUND(C35-D35,2))</f>
         <v/>
       </c>
       <c r="F35" s="12" t="n"/>
@@ -3281,7 +3281,7 @@
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="12" t="n"/>
       <c r="E36" s="14">
-        <f>IF(OR(C36="",D36=""),"",C36-D36)</f>
+        <f>IF(OR(C36="",D36=""),"",ROUND(C36-D36,2))</f>
         <v/>
       </c>
       <c r="F36" s="12" t="n"/>
@@ -3306,7 +3306,7 @@
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="12" t="n"/>
       <c r="E37" s="14">
-        <f>IF(OR(C37="",D37=""),"",C37-D37)</f>
+        <f>IF(OR(C37="",D37=""),"",ROUND(C37-D37,2))</f>
         <v/>
       </c>
       <c r="F37" s="12" t="n"/>
@@ -3331,7 +3331,7 @@
       <c r="C38" s="12" t="n"/>
       <c r="D38" s="12" t="n"/>
       <c r="E38" s="14">
-        <f>IF(OR(C38="",D38=""),"",C38-D38)</f>
+        <f>IF(OR(C38="",D38=""),"",ROUND(C38-D38,2))</f>
         <v/>
       </c>
       <c r="F38" s="12" t="n"/>
@@ -3356,7 +3356,7 @@
       <c r="C39" s="12" t="n"/>
       <c r="D39" s="12" t="n"/>
       <c r="E39" s="14">
-        <f>IF(OR(C39="",D39=""),"",C39-D39)</f>
+        <f>IF(OR(C39="",D39=""),"",ROUND(C39-D39,2))</f>
         <v/>
       </c>
       <c r="F39" s="12" t="n"/>
@@ -3381,7 +3381,7 @@
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="12" t="n"/>
       <c r="E40" s="14">
-        <f>IF(OR(C40="",D40=""),"",C40-D40)</f>
+        <f>IF(OR(C40="",D40=""),"",ROUND(C40-D40,2))</f>
         <v/>
       </c>
       <c r="F40" s="12" t="n"/>
@@ -3406,7 +3406,7 @@
       <c r="C41" s="12" t="n"/>
       <c r="D41" s="12" t="n"/>
       <c r="E41" s="14">
-        <f>IF(OR(C41="",D41=""),"",C41-D41)</f>
+        <f>IF(OR(C41="",D41=""),"",ROUND(C41-D41,2))</f>
         <v/>
       </c>
       <c r="F41" s="12" t="n"/>
@@ -3431,7 +3431,7 @@
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="12" t="n"/>
       <c r="E42" s="14">
-        <f>IF(OR(C42="",D42=""),"",C42-D42)</f>
+        <f>IF(OR(C42="",D42=""),"",ROUND(C42-D42,2))</f>
         <v/>
       </c>
       <c r="F42" s="12" t="n"/>
@@ -3456,7 +3456,7 @@
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="12" t="n"/>
       <c r="E43" s="14">
-        <f>IF(OR(C43="",D43=""),"",C43-D43)</f>
+        <f>IF(OR(C43="",D43=""),"",ROUND(C43-D43,2))</f>
         <v/>
       </c>
       <c r="F43" s="12" t="n"/>
@@ -3481,7 +3481,7 @@
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="12" t="n"/>
       <c r="E44" s="14">
-        <f>IF(OR(C44="",D44=""),"",C44-D44)</f>
+        <f>IF(OR(C44="",D44=""),"",ROUND(C44-D44,2))</f>
         <v/>
       </c>
       <c r="F44" s="12" t="n"/>
@@ -3506,7 +3506,7 @@
       <c r="C45" s="12" t="n"/>
       <c r="D45" s="12" t="n"/>
       <c r="E45" s="14">
-        <f>IF(OR(C45="",D45=""),"",C45-D45)</f>
+        <f>IF(OR(C45="",D45=""),"",ROUND(C45-D45,2))</f>
         <v/>
       </c>
       <c r="F45" s="12" t="n"/>
@@ -3531,7 +3531,7 @@
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="12" t="n"/>
       <c r="E46" s="14">
-        <f>IF(OR(C46="",D46=""),"",C46-D46)</f>
+        <f>IF(OR(C46="",D46=""),"",ROUND(C46-D46,2))</f>
         <v/>
       </c>
       <c r="F46" s="12" t="n"/>
@@ -3556,7 +3556,7 @@
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="12" t="n"/>
       <c r="E47" s="14">
-        <f>IF(OR(C47="",D47=""),"",C47-D47)</f>
+        <f>IF(OR(C47="",D47=""),"",ROUND(C47-D47,2))</f>
         <v/>
       </c>
       <c r="F47" s="12" t="n"/>
@@ -3581,7 +3581,7 @@
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="12" t="n"/>
       <c r="E48" s="14">
-        <f>IF(OR(C48="",D48=""),"",C48-D48)</f>
+        <f>IF(OR(C48="",D48=""),"",ROUND(C48-D48,2))</f>
         <v/>
       </c>
       <c r="F48" s="12" t="n"/>
@@ -3606,7 +3606,7 @@
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="12" t="n"/>
       <c r="E49" s="14">
-        <f>IF(OR(C49="",D49=""),"",C49-D49)</f>
+        <f>IF(OR(C49="",D49=""),"",ROUND(C49-D49,2))</f>
         <v/>
       </c>
       <c r="F49" s="12" t="n"/>
@@ -3631,7 +3631,7 @@
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="12" t="n"/>
       <c r="E50" s="14">
-        <f>IF(OR(C50="",D50=""),"",C50-D50)</f>
+        <f>IF(OR(C50="",D50=""),"",ROUND(C50-D50,2))</f>
         <v/>
       </c>
       <c r="F50" s="12" t="n"/>
@@ -3656,7 +3656,7 @@
       <c r="C51" s="12" t="n"/>
       <c r="D51" s="12" t="n"/>
       <c r="E51" s="14">
-        <f>IF(OR(C51="",D51=""),"",C51-D51)</f>
+        <f>IF(OR(C51="",D51=""),"",ROUND(C51-D51,2))</f>
         <v/>
       </c>
       <c r="F51" s="12" t="n"/>
@@ -3681,7 +3681,7 @@
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="12" t="n"/>
       <c r="E52" s="14">
-        <f>IF(OR(C52="",D52=""),"",C52-D52)</f>
+        <f>IF(OR(C52="",D52=""),"",ROUND(C52-D52,2))</f>
         <v/>
       </c>
       <c r="F52" s="12" t="n"/>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <f>COUNTIFS(B5:B52,"ensaio",H5:H52,"&lt;&gt;")</f>
+        <f>COUNTIFS(B5:B52,"ensaio",H5:H52,"APROVADO")+COUNTIFS(B5:B52,"ensaio",H5:H52,"REPROVADO")</f>
         <v/>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="18">
-        <f>IF(OR(D5="",K5=""),"",D5-K5)</f>
+        <f>IF(OR(D5="",K5=""),"",ROUND(D5-K5,2))</f>
         <v/>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="18">
-        <f>IF(OR(D6="",K6=""),"",D6-K6)</f>
+        <f>IF(OR(D6="",K6=""),"",ROUND(D6-K6,2))</f>
         <v/>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="18">
-        <f>IF(OR(D7="",K7=""),"",D7-K7)</f>
+        <f>IF(OR(D7="",K7=""),"",ROUND(D7-K7,2))</f>
         <v/>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="18">
-        <f>IF(OR(D8="",K8=""),"",D8-K8)</f>
+        <f>IF(OR(D8="",K8=""),"",ROUND(D8-K8,2))</f>
         <v/>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="18">
-        <f>IF(OR(D9="",K9=""),"",D9-K9)</f>
+        <f>IF(OR(D9="",K9=""),"",ROUND(D9-K9,2))</f>
         <v/>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="18">
-        <f>IF(OR(D10="",K10=""),"",D10-K10)</f>
+        <f>IF(OR(D10="",K10=""),"",ROUND(D10-K10,2))</f>
         <v/>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="18">
-        <f>IF(OR(D11="",K11=""),"",D11-K11)</f>
+        <f>IF(OR(D11="",K11=""),"",ROUND(D11-K11,2))</f>
         <v/>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="18">
-        <f>IF(OR(D12="",K12=""),"",D12-K12)</f>
+        <f>IF(OR(D12="",K12=""),"",ROUND(D12-K12,2))</f>
         <v/>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="18">
-        <f>IF(OR(D13="",K13=""),"",D13-K13)</f>
+        <f>IF(OR(D13="",K13=""),"",ROUND(D13-K13,2))</f>
         <v/>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="18">
-        <f>IF(OR(D14="",K14=""),"",D14-K14)</f>
+        <f>IF(OR(D14="",K14=""),"",ROUND(D14-K14,2))</f>
         <v/>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="18">
-        <f>IF(OR(D15="",K15=""),"",D15-K15)</f>
+        <f>IF(OR(D15="",K15=""),"",ROUND(D15-K15,2))</f>
         <v/>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="18">
-        <f>IF(OR(D16="",K16=""),"",D16-K16)</f>
+        <f>IF(OR(D16="",K16=""),"",ROUND(D16-K16,2))</f>
         <v/>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="18">
-        <f>IF(OR(D17="",K17=""),"",D17-K17)</f>
+        <f>IF(OR(D17="",K17=""),"",ROUND(D17-K17,2))</f>
         <v/>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="18">
-        <f>IF(OR(D18="",K18=""),"",D18-K18)</f>
+        <f>IF(OR(D18="",K18=""),"",ROUND(D18-K18,2))</f>
         <v/>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="18">
-        <f>IF(OR(D19="",K19=""),"",D19-K19)</f>
+        <f>IF(OR(D19="",K19=""),"",ROUND(D19-K19,2))</f>
         <v/>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="18">
-        <f>IF(OR(D20="",K20=""),"",D20-K20)</f>
+        <f>IF(OR(D20="",K20=""),"",ROUND(D20-K20,2))</f>
         <v/>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="B24" s="18">
-        <f>IFERROR(AVERAGE(L5:L7),"")</f>
+        <f>IFERROR(ROUND(AVERAGE(L5:L7),2),"")</f>
         <v/>
       </c>
       <c r="C24" s="18">
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="B25" s="18">
-        <f>IFERROR(AVERAGE(L9:L11),"")</f>
+        <f>IFERROR(ROUND(AVERAGE(L9:L11),2),"")</f>
         <v/>
       </c>
       <c r="C25" s="18">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="B26" s="18">
-        <f>IFERROR(AVERAGE(L13:L15),"")</f>
+        <f>IFERROR(ROUND(AVERAGE(L13:L15),2),"")</f>
         <v/>
       </c>
       <c r="C26" s="18">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B27" s="18">
-        <f>IFERROR(AVERAGE(L17:L19),"")</f>
+        <f>IFERROR(ROUND(AVERAGE(L17:L19),2),"")</f>
         <v/>
       </c>
       <c r="C27" s="18">
@@ -5801,7 +5801,7 @@
         <v>214920</v>
       </c>
       <c r="F5" s="15">
-        <f>_xlfn.CONCAT(COUNTIFS('E1-Vazamento'!$B$5:$B$16,"ensaio",'E1-Vazamento'!$H$5:$H$16,"APROVADO")," / ",COUNTIFS('E1-Vazamento'!$B$5:$B$16,"ensaio",'E1-Vazamento'!$H$5:$H$16,"&lt;&gt;"))</f>
+        <f>COUNTIFS('E1-Vazamento'!$B$5:$B$16,"ensaio",'E1-Vazamento'!$H$5:$H$16,"APROVADO")&amp;" / "&amp;(COUNTIFS('E1-Vazamento'!$B$5:$B$16,"ensaio",'E1-Vazamento'!$H$5:$H$16,"APROVADO")+COUNTIFS('E1-Vazamento'!$B$5:$B$16,"ensaio",'E1-Vazamento'!$H$5:$H$16,"REPROVADO"))</f>
         <v/>
       </c>
       <c r="G5" s="19">
@@ -5832,7 +5832,7 @@
         <v>103568</v>
       </c>
       <c r="F6" s="15">
-        <f>_xlfn.CONCAT(COUNTIFS('E1-Vazamento'!$B$17:$B$28,"ensaio",'E1-Vazamento'!$H$17:$H$28,"APROVADO")," / ",COUNTIFS('E1-Vazamento'!$B$17:$B$28,"ensaio",'E1-Vazamento'!$H$17:$H$28,"&lt;&gt;"))</f>
+        <f>COUNTIFS('E1-Vazamento'!$B$17:$B$28,"ensaio",'E1-Vazamento'!$H$17:$H$28,"APROVADO")&amp;" / "&amp;(COUNTIFS('E1-Vazamento'!$B$17:$B$28,"ensaio",'E1-Vazamento'!$H$17:$H$28,"APROVADO")+COUNTIFS('E1-Vazamento'!$B$17:$B$28,"ensaio",'E1-Vazamento'!$H$17:$H$28,"REPROVADO"))</f>
         <v/>
       </c>
       <c r="G6" s="19">
@@ -5863,7 +5863,7 @@
         <v>227505</v>
       </c>
       <c r="F7" s="15">
-        <f>_xlfn.CONCAT(COUNTIFS('E1-Vazamento'!$B$29:$B$40,"ensaio",'E1-Vazamento'!$H$29:$H$40,"APROVADO")," / ",COUNTIFS('E1-Vazamento'!$B$29:$B$40,"ensaio",'E1-Vazamento'!$H$29:$H$40,"&lt;&gt;"))</f>
+        <f>COUNTIFS('E1-Vazamento'!$B$29:$B$40,"ensaio",'E1-Vazamento'!$H$29:$H$40,"APROVADO")&amp;" / "&amp;(COUNTIFS('E1-Vazamento'!$B$29:$B$40,"ensaio",'E1-Vazamento'!$H$29:$H$40,"APROVADO")+COUNTIFS('E1-Vazamento'!$B$29:$B$40,"ensaio",'E1-Vazamento'!$H$29:$H$40,"REPROVADO"))</f>
         <v/>
       </c>
       <c r="G7" s="19">
@@ -5894,7 +5894,7 @@
         <v>276635</v>
       </c>
       <c r="F8" s="15">
-        <f>_xlfn.CONCAT(COUNTIFS('E1-Vazamento'!$B$41:$B$52,"ensaio",'E1-Vazamento'!$H$41:$H$52,"APROVADO")," / ",COUNTIFS('E1-Vazamento'!$B$41:$B$52,"ensaio",'E1-Vazamento'!$H$41:$H$52,"&lt;&gt;"))</f>
+        <f>COUNTIFS('E1-Vazamento'!$B$41:$B$52,"ensaio",'E1-Vazamento'!$H$41:$H$52,"APROVADO")&amp;" / "&amp;(COUNTIFS('E1-Vazamento'!$B$41:$B$52,"ensaio",'E1-Vazamento'!$H$41:$H$52,"APROVADO")+COUNTIFS('E1-Vazamento'!$B$41:$B$52,"ensaio",'E1-Vazamento'!$H$41:$H$52,"REPROVADO"))</f>
         <v/>
       </c>
       <c r="G8" s="19">
